--- a/AAPL_Model.xlsx
+++ b/AAPL_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72883B8-0766-4829-864E-2C6DF766B868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFAAF7B-7DFE-4FA2-97AC-88B8B6D0FEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="12435" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4813,10 +4813,10 @@
     <t>It is among the most valuable and recognizable brands worldwide … their PP&amp;E is $48 billion and they generate ~$100 billion in net income annually … incredible … $3.5 trillion dollars of market cap from a company kept alive by Microsoft as to avoid regulatory anti-trust scrutiny</t>
   </si>
   <si>
-    <t>12/3/25</t>
-  </si>
-  <si>
     <t>Q3'25</t>
+  </si>
+  <si>
+    <t>1/10/2026</t>
   </si>
 </sst>
 </file>
@@ -5197,7 +5197,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5350,9 +5350,6 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -15101,10 +15098,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="43">
-        <v>284.22000000000003</v>
+        <v>259.37</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="4" spans="2:17">
@@ -15115,7 +15112,7 @@
         <v>14840</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="5" spans="2:17">
@@ -15124,7 +15121,7 @@
       </c>
       <c r="C5" s="59">
         <f>C3*C4</f>
-        <v>4217824.8000000007</v>
+        <v>3849050.8000000003</v>
       </c>
     </row>
     <row r="6" spans="2:17">
@@ -15136,7 +15133,7 @@
         <v>55372</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="7" spans="2:17">
@@ -15148,7 +15145,7 @@
         <v>91775</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="8" spans="2:17">
@@ -15157,7 +15154,7 @@
       </c>
       <c r="C8" s="60">
         <f>C5-C6+C7</f>
-        <v>4254227.8000000007</v>
+        <v>3885453.8000000003</v>
       </c>
     </row>
     <row r="10" spans="2:17" ht="15">
@@ -15461,9 +15458,6 @@
     <hyperlink ref="P14" r:id="rId2" xr:uid="{CE68CDAE-8042-4939-BB57-CC6215F339BE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3" twoDigitTextYear="1"/>
-  </ignoredErrors>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
@@ -15482,7 +15476,7 @@
     <col min="75" max="94" width="9.140625" style="1"/>
     <col min="95" max="95" width="9.140625" style="35"/>
     <col min="96" max="104" width="9.140625" style="35" customWidth="1"/>
-    <col min="105" max="105" width="11.5703125" style="35" customWidth="1"/>
+    <col min="105" max="105" width="13.140625" style="35" customWidth="1"/>
     <col min="106" max="156" width="9.140625" style="35"/>
     <col min="157" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -16168,39 +16162,39 @@
       </c>
       <c r="CS4" s="74">
         <f t="shared" si="8"/>
-        <v>246708.92024999997</v>
+        <v>244455.87074999997</v>
       </c>
       <c r="CT4" s="74">
         <f t="shared" si="8"/>
-        <v>263978.54466749995</v>
+        <v>261567.78170249998</v>
       </c>
       <c r="CU4" s="74">
         <f t="shared" si="8"/>
-        <v>281137.15007088747</v>
+        <v>278569.68751316244</v>
       </c>
       <c r="CV4" s="74">
         <f t="shared" si="8"/>
-        <v>298005.37907514075</v>
+        <v>295283.86876395222</v>
       </c>
       <c r="CW4" s="74">
         <f t="shared" si="8"/>
-        <v>314395.67492427345</v>
+        <v>311524.48154596955</v>
       </c>
       <c r="CX4" s="74">
         <f t="shared" si="8"/>
-        <v>328543.48029586574</v>
+        <v>325543.08321553818</v>
       </c>
       <c r="CY4" s="74">
         <f t="shared" si="8"/>
-        <v>341685.21950770036</v>
+        <v>338564.80654415971</v>
       </c>
       <c r="CZ4" s="74">
         <f t="shared" si="8"/>
-        <v>351935.7760929314</v>
+        <v>348721.75074048451</v>
       </c>
       <c r="DA4" s="74">
         <f t="shared" si="8"/>
-        <v>358974.49161479005</v>
+        <v>355696.18575529422</v>
       </c>
     </row>
     <row r="5" spans="2:157">
@@ -16326,39 +16320,39 @@
       </c>
       <c r="CS5" s="74">
         <f t="shared" si="9"/>
-        <v>40773.196800000012</v>
+        <v>41150.726400000007</v>
       </c>
       <c r="CT5" s="74">
         <f t="shared" si="9"/>
-        <v>45665.98041600002</v>
+        <v>46088.813568000012</v>
       </c>
       <c r="CU5" s="74">
         <f t="shared" si="9"/>
-        <v>49775.918653440029</v>
+        <v>50236.806789120019</v>
       </c>
       <c r="CV5" s="74">
         <f t="shared" si="9"/>
-        <v>53260.23295918083</v>
+        <v>53753.383264358425</v>
       </c>
       <c r="CW5" s="74">
         <f t="shared" si="9"/>
-        <v>56455.846936731679</v>
+        <v>56978.586260219934</v>
       </c>
       <c r="CX5" s="74">
         <f t="shared" si="9"/>
-        <v>59278.639283568264</v>
+        <v>59827.515573230936</v>
       </c>
       <c r="CY5" s="74">
         <f t="shared" si="9"/>
-        <v>61946.178051328832</v>
+        <v>62519.753774026321</v>
       </c>
       <c r="CZ5" s="74">
         <f t="shared" si="9"/>
-        <v>64424.02517338199</v>
+        <v>65020.543924987374</v>
       </c>
       <c r="DA5" s="74">
         <f t="shared" si="9"/>
-        <v>66678.866054450351</v>
+        <v>67296.262962361929</v>
       </c>
     </row>
     <row r="6" spans="2:157">
@@ -16800,39 +16794,39 @@
       </c>
       <c r="CS8" s="74">
         <f t="shared" si="12"/>
-        <v>143106.13800000001</v>
+        <v>140617.33559999999</v>
       </c>
       <c r="CT8" s="74">
         <f t="shared" si="12"/>
-        <v>161709.93594</v>
+        <v>157491.41587200001</v>
       </c>
       <c r="CU8" s="74">
         <f t="shared" si="12"/>
-        <v>179498.02889340001</v>
+        <v>173240.55745920003</v>
       </c>
       <c r="CV8" s="74">
         <f t="shared" si="12"/>
-        <v>195652.85149380603</v>
+        <v>187099.80205593604</v>
       </c>
       <c r="CW8" s="74">
         <f t="shared" si="12"/>
-        <v>211305.07961331052</v>
+        <v>200196.78819985158</v>
       </c>
       <c r="CX8" s="74">
         <f t="shared" si="12"/>
-        <v>226096.43518624228</v>
+        <v>212208.59549184269</v>
       </c>
       <c r="CY8" s="74">
         <f t="shared" si="12"/>
-        <v>239662.22129741684</v>
+        <v>222819.02526643482</v>
       </c>
       <c r="CZ8" s="74">
         <f t="shared" si="12"/>
-        <v>251645.33236228768</v>
+        <v>231731.78627709224</v>
       </c>
       <c r="DA8" s="74">
         <f t="shared" si="12"/>
-        <v>261711.1456567792</v>
+        <v>238683.73986540502</v>
       </c>
     </row>
     <row r="9" spans="2:157" s="2" customFormat="1" ht="15">
@@ -16980,39 +16974,39 @@
       </c>
       <c r="CS9" s="75">
         <f t="shared" si="15"/>
-        <v>495495.49725000001</v>
+        <v>491131.17495000002</v>
       </c>
       <c r="CT9" s="75">
         <f t="shared" si="15"/>
-        <v>536495.85971549992</v>
+        <v>530289.40983450005</v>
       </c>
       <c r="CU9" s="75">
         <f t="shared" si="15"/>
-        <v>577206.44043972751</v>
+        <v>568842.39458348253</v>
       </c>
       <c r="CV9" s="75">
         <f t="shared" si="15"/>
-        <v>615411.36284741235</v>
+        <v>604629.95340353157</v>
       </c>
       <c r="CW9" s="75">
         <f t="shared" si="15"/>
-        <v>652391.85791005625</v>
+        <v>638935.11244178168</v>
       </c>
       <c r="CX9" s="75">
         <f t="shared" si="15"/>
-        <v>685239.83786974661</v>
+        <v>668900.47738468205</v>
       </c>
       <c r="CY9" s="75">
         <f t="shared" si="15"/>
-        <v>715719.46237760875</v>
+        <v>696329.42910578358</v>
       </c>
       <c r="CZ9" s="75">
         <f t="shared" si="15"/>
-        <v>741155.23558497545</v>
+        <v>718624.18289893842</v>
       </c>
       <c r="DA9" s="75">
         <f t="shared" ref="DA9" si="16">SUM(DA4:DA8)</f>
-        <v>761246.10630195762</v>
+        <v>735557.79155899922</v>
       </c>
       <c r="DB9" s="34"/>
       <c r="DC9" s="34"/>
@@ -17194,7 +17188,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="CS11" s="72">
-        <v>9.5000000000000001E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="CT11" s="72">
         <v>7.0000000000000007E-2</v>
@@ -17345,7 +17339,7 @@
         <v>0.12</v>
       </c>
       <c r="CS12" s="72">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="CT12" s="72">
         <v>0.12</v>
@@ -17798,31 +17792,31 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="CS15" s="72">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="CT15" s="72">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="CU15" s="72">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="CV15" s="72">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="CW15" s="72">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="CX15" s="72">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="CY15" s="72">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="CZ15" s="72">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DA15" s="72">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="16" spans="2:157" s="2" customFormat="1" ht="15">
@@ -18160,39 +18154,39 @@
       </c>
       <c r="CS16" s="73">
         <f t="shared" si="30"/>
-        <v>9.9159256979336474E-2</v>
+        <v>8.9477866768708614E-2</v>
       </c>
       <c r="CT16" s="73">
         <f t="shared" si="30"/>
-        <v>8.2746185773739489E-2</v>
+        <v>7.973070511862046E-2</v>
       </c>
       <c r="CU16" s="73">
         <f t="shared" si="30"/>
-        <v>7.5882376325916434E-2</v>
+        <v>7.2701781393323728E-2</v>
       </c>
       <c r="CV16" s="73">
         <f t="shared" si="30"/>
-        <v>6.6189355715746245E-2</v>
+        <v>6.2912960005826246E-2</v>
       </c>
       <c r="CW16" s="73">
         <f t="shared" si="30"/>
-        <v>6.0090692657251088E-2</v>
+        <v>5.6737445515463447E-2</v>
       </c>
       <c r="CX16" s="73">
         <f t="shared" si="30"/>
-        <v>5.0350076509107833E-2</v>
+        <v>4.6898917213022528E-2</v>
       </c>
       <c r="CY16" s="73">
         <f t="shared" si="30"/>
-        <v>4.4480228415522793E-2</v>
+        <v>4.1006028024296537E-2</v>
       </c>
       <c r="CZ16" s="73">
         <f t="shared" si="30"/>
-        <v>3.5538747434461948E-2</v>
+        <v>3.2017537764827075E-2</v>
       </c>
       <c r="DA16" s="73">
         <f t="shared" si="30"/>
-        <v>2.7107506973387263E-2</v>
+        <v>2.3563928215928343E-2</v>
       </c>
       <c r="DB16" s="34"/>
       <c r="DC16" s="34"/>
@@ -21472,39 +21466,39 @@
       </c>
       <c r="CS44" s="75">
         <f t="shared" ref="CS44:DA44" si="90">CS9</f>
-        <v>495495.49725000001</v>
+        <v>491131.17495000002</v>
       </c>
       <c r="CT44" s="75">
         <f t="shared" si="90"/>
-        <v>536495.85971549992</v>
+        <v>530289.40983450005</v>
       </c>
       <c r="CU44" s="75">
         <f t="shared" si="90"/>
-        <v>577206.44043972751</v>
+        <v>568842.39458348253</v>
       </c>
       <c r="CV44" s="75">
         <f t="shared" si="90"/>
-        <v>615411.36284741235</v>
+        <v>604629.95340353157</v>
       </c>
       <c r="CW44" s="75">
         <f t="shared" si="90"/>
-        <v>652391.85791005625</v>
+        <v>638935.11244178168</v>
       </c>
       <c r="CX44" s="75">
         <f t="shared" si="90"/>
-        <v>685239.83786974661</v>
+        <v>668900.47738468205</v>
       </c>
       <c r="CY44" s="75">
         <f t="shared" si="90"/>
-        <v>715719.46237760875</v>
+        <v>696329.42910578358</v>
       </c>
       <c r="CZ44" s="75">
         <f t="shared" si="90"/>
-        <v>741155.23558497545</v>
+        <v>718624.18289893842</v>
       </c>
       <c r="DA44" s="75">
         <f t="shared" si="90"/>
-        <v>761246.10630195762</v>
+        <v>735557.79155899922</v>
       </c>
       <c r="DB44" s="34"/>
       <c r="DC44" s="34"/>
@@ -21840,39 +21834,39 @@
       </c>
       <c r="CS45" s="35">
         <f t="shared" ref="CS45:DA45" si="94">CS44*(1-CS57)</f>
-        <v>261621.62254800001</v>
+        <v>259317.26037360003</v>
       </c>
       <c r="CT45" s="35">
         <f t="shared" si="94"/>
-        <v>282196.82221035298</v>
+        <v>278932.22957294702</v>
       </c>
       <c r="CU45" s="35">
         <f t="shared" si="94"/>
-        <v>302456.17479041725</v>
+        <v>298073.41476174485</v>
       </c>
       <c r="CV45" s="35">
         <f t="shared" si="94"/>
-        <v>321244.73140634928</v>
+        <v>315616.83567664347</v>
       </c>
       <c r="CW45" s="35">
         <f t="shared" si="94"/>
-        <v>339243.76611322927</v>
+        <v>332246.25846972648</v>
       </c>
       <c r="CX45" s="35">
         <f t="shared" si="94"/>
-        <v>355639.47585439851</v>
+        <v>347159.34776265</v>
       </c>
       <c r="CY45" s="35">
         <f t="shared" si="94"/>
-        <v>370742.68151160137</v>
+        <v>360698.64427679591</v>
       </c>
       <c r="CZ45" s="35">
         <f t="shared" si="94"/>
-        <v>383177.25679743232</v>
+        <v>371528.70255875116</v>
       </c>
       <c r="DA45" s="74">
         <f t="shared" si="94"/>
-        <v>392802.99085181014</v>
+        <v>379547.82044444361</v>
       </c>
     </row>
     <row r="46" spans="2:156">
@@ -22225,39 +22219,39 @@
       </c>
       <c r="CS46" s="74">
         <f t="shared" ref="CS46:DA46" si="98">CS44-CS45</f>
-        <v>233873.874702</v>
+        <v>231813.91457639998</v>
       </c>
       <c r="CT46" s="74">
         <f t="shared" si="98"/>
-        <v>254299.03750514693</v>
+        <v>251357.18026155303</v>
       </c>
       <c r="CU46" s="74">
         <f t="shared" si="98"/>
-        <v>274750.26564931025</v>
+        <v>270768.97982173768</v>
       </c>
       <c r="CV46" s="74">
         <f t="shared" si="98"/>
-        <v>294166.63144106307</v>
+        <v>289013.1177268881</v>
       </c>
       <c r="CW46" s="74">
         <f t="shared" si="98"/>
-        <v>313148.09179682698</v>
+        <v>306688.85397205519</v>
       </c>
       <c r="CX46" s="74">
         <f t="shared" si="98"/>
-        <v>329600.3620153481</v>
+        <v>321741.12962203205</v>
       </c>
       <c r="CY46" s="74">
         <f t="shared" si="98"/>
-        <v>344976.78086600738</v>
+        <v>335630.78482898767</v>
       </c>
       <c r="CZ46" s="74">
         <f t="shared" si="98"/>
-        <v>357977.97878754314</v>
+        <v>347095.48034018726</v>
       </c>
       <c r="DA46" s="74">
         <f t="shared" si="98"/>
-        <v>368443.11545014748</v>
+        <v>356009.97111455561</v>
       </c>
     </row>
     <row r="47" spans="2:156">
@@ -22542,39 +22536,39 @@
       </c>
       <c r="CS47" s="74">
         <f t="shared" ref="CS47:DA47" si="99">CS44*CS58</f>
-        <v>42117.117266250003</v>
+        <v>41746.149870750007</v>
       </c>
       <c r="CT47" s="74">
         <f t="shared" si="99"/>
-        <v>48284.627374394993</v>
+        <v>47726.046885105003</v>
       </c>
       <c r="CU47" s="74">
         <f t="shared" si="99"/>
-        <v>47619.53133627752</v>
+        <v>46929.497553137313</v>
       </c>
       <c r="CV47" s="74">
         <f t="shared" si="99"/>
-        <v>46155.852213555925</v>
+        <v>45347.246505264869</v>
       </c>
       <c r="CW47" s="74">
         <f t="shared" si="99"/>
-        <v>46972.213769524045</v>
+        <v>46003.328095808276</v>
       </c>
       <c r="CX47" s="74">
         <f t="shared" si="99"/>
-        <v>47966.78865088227</v>
+        <v>46823.033416927748</v>
       </c>
       <c r="CY47" s="74">
         <f t="shared" si="99"/>
-        <v>48668.923441677398</v>
+        <v>47350.401179193286</v>
       </c>
       <c r="CZ47" s="74">
         <f t="shared" si="99"/>
-        <v>48916.245548608385</v>
+        <v>47429.196071329941</v>
       </c>
       <c r="DA47" s="74">
         <f t="shared" si="99"/>
-        <v>49480.996909627247</v>
+        <v>47811.25645133495</v>
       </c>
     </row>
     <row r="48" spans="2:156">
@@ -22859,39 +22853,39 @@
       </c>
       <c r="CS48" s="74">
         <f t="shared" ref="CS48:DA48" si="100">CS44*CS59</f>
-        <v>33160.738175064434</v>
+        <v>32868.658529729379</v>
       </c>
       <c r="CT48" s="74">
         <f t="shared" si="100"/>
-        <v>35904.662776492645</v>
+        <v>35489.299850607866</v>
       </c>
       <c r="CU48" s="74">
         <f t="shared" si="100"/>
-        <v>38629.193909153582</v>
+        <v>38069.43517014887</v>
       </c>
       <c r="CV48" s="74">
         <f t="shared" si="100"/>
-        <v>41186.035365819087</v>
+        <v>40464.49602245284</v>
       </c>
       <c r="CW48" s="74">
         <f t="shared" si="100"/>
-        <v>43660.932758757197</v>
+        <v>42760.34816083745</v>
       </c>
       <c r="CX48" s="74">
         <f t="shared" si="100"/>
-        <v>45859.264063619637</v>
+        <v>44765.762189232584</v>
       </c>
       <c r="CY48" s="74">
         <f t="shared" si="100"/>
-        <v>47899.094604137215</v>
+        <v>46601.428288093244</v>
       </c>
       <c r="CZ48" s="74">
         <f t="shared" si="100"/>
-        <v>49601.368429613045</v>
+        <v>48093.491278202149</v>
       </c>
       <c r="DA48" s="74">
         <f t="shared" si="100"/>
-        <v>50945.937870208334</v>
+        <v>49226.762854335087</v>
       </c>
     </row>
     <row r="49" spans="2:156">
@@ -23244,39 +23238,39 @@
       </c>
       <c r="CS49" s="74">
         <f t="shared" ref="CS49:DA49" si="103">CS46-SUM(CS47:CS48)</f>
-        <v>158596.01926068557</v>
+        <v>157199.10617592061</v>
       </c>
       <c r="CT49" s="74">
         <f t="shared" si="103"/>
-        <v>170109.74735425931</v>
+        <v>168141.83352584016</v>
       </c>
       <c r="CU49" s="74">
         <f t="shared" si="103"/>
-        <v>188501.54040387916</v>
+        <v>185770.0470984515</v>
       </c>
       <c r="CV49" s="74">
         <f t="shared" si="103"/>
-        <v>206824.74386168807</v>
+        <v>203201.37519917038</v>
       </c>
       <c r="CW49" s="74">
         <f t="shared" si="103"/>
-        <v>222514.94526854574</v>
+        <v>217925.17771540946</v>
       </c>
       <c r="CX49" s="74">
         <f t="shared" si="103"/>
-        <v>235774.30930084619</v>
+        <v>230152.33401587172</v>
       </c>
       <c r="CY49" s="74">
         <f t="shared" si="103"/>
-        <v>248408.76282019276</v>
+        <v>241678.95536170114</v>
       </c>
       <c r="CZ49" s="74">
         <f t="shared" si="103"/>
-        <v>259460.36480932171</v>
+        <v>251572.79299065517</v>
       </c>
       <c r="DA49" s="74">
         <f t="shared" si="103"/>
-        <v>268016.18067031191</v>
+        <v>258971.95180888555</v>
       </c>
     </row>
     <row r="50" spans="2:156">
@@ -23557,43 +23551,43 @@
       </c>
       <c r="CR50" s="74">
         <f>CQ64*($DA$66)</f>
-        <v>7366.4699999999993</v>
+        <v>7276.6350000000002</v>
       </c>
       <c r="CS50" s="74">
         <f t="shared" ref="CS50:DA50" si="104">CR64*($DA$66)-(10000*(0.035))</f>
-        <v>32683.160014161913</v>
+        <v>32265.399497605064</v>
       </c>
       <c r="CT50" s="74">
         <f t="shared" si="104"/>
-        <v>64837.190050263773</v>
+        <v>63725.980664694012</v>
       </c>
       <c r="CU50" s="74">
         <f t="shared" si="104"/>
-        <v>104331.77022796409</v>
+        <v>102227.63121103222</v>
       </c>
       <c r="CV50" s="74">
         <f t="shared" si="104"/>
-        <v>153557.04974517695</v>
+        <v>150049.64569432201</v>
       </c>
       <c r="CW50" s="74">
         <f t="shared" si="104"/>
-        <v>214137.22925049099</v>
+        <v>208706.97771368638</v>
       </c>
       <c r="CX50" s="74">
         <f t="shared" si="104"/>
-        <v>287538.45978714107</v>
+        <v>279549.24712268775</v>
       </c>
       <c r="CY50" s="74">
         <f t="shared" si="104"/>
-        <v>375507.3362708317</v>
+        <v>364185.19467074558</v>
       </c>
       <c r="CZ50" s="74">
         <f t="shared" si="104"/>
-        <v>480387.63252803293</v>
+        <v>464788.93678363337</v>
       </c>
       <c r="DA50" s="74">
         <f t="shared" si="104"/>
-        <v>604756.08088044228</v>
+        <v>583740.80201265402</v>
       </c>
     </row>
     <row r="51" spans="2:156">
@@ -23942,43 +23936,43 @@
       </c>
       <c r="CR51" s="74">
         <f>CR49+CR50</f>
-        <v>152687.03161309884</v>
+        <v>152597.19661309884</v>
       </c>
       <c r="CS51" s="74">
         <f t="shared" ref="CS51:DA51" si="107">CS49+CS50</f>
-        <v>191279.1792748475</v>
+        <v>189464.50567352568</v>
       </c>
       <c r="CT51" s="74">
         <f t="shared" si="107"/>
-        <v>234946.93740452308</v>
+        <v>231867.81419053418</v>
       </c>
       <c r="CU51" s="74">
         <f t="shared" si="107"/>
-        <v>292833.31063184328</v>
+        <v>287997.67830948369</v>
       </c>
       <c r="CV51" s="74">
         <f t="shared" si="107"/>
-        <v>360381.79360686499</v>
+        <v>353251.02089349239</v>
       </c>
       <c r="CW51" s="74">
         <f t="shared" si="107"/>
-        <v>436652.17451903672</v>
+        <v>426632.15542909584</v>
       </c>
       <c r="CX51" s="74">
         <f t="shared" si="107"/>
-        <v>523312.76908798725</v>
+        <v>509701.5811385595</v>
       </c>
       <c r="CY51" s="74">
         <f t="shared" si="107"/>
-        <v>623916.09909102449</v>
+        <v>605864.15003244672</v>
       </c>
       <c r="CZ51" s="74">
         <f t="shared" si="107"/>
-        <v>739847.99733735458</v>
+        <v>716361.7297742886</v>
       </c>
       <c r="DA51" s="74">
         <f t="shared" si="107"/>
-        <v>872772.26155075419</v>
+        <v>842712.75382153958</v>
       </c>
     </row>
     <row r="52" spans="2:156">
@@ -24259,43 +24253,43 @@
       </c>
       <c r="CR52" s="74">
         <f>CR51*CR61</f>
-        <v>27483.66569035779</v>
+        <v>27467.495390357792</v>
       </c>
       <c r="CS52" s="74">
         <f t="shared" ref="CS52:DA52" si="108">CS51*CS61</f>
-        <v>34430.252269472549</v>
+        <v>34103.611021234625</v>
       </c>
       <c r="CT52" s="74">
         <f t="shared" si="108"/>
-        <v>42290.448732814155</v>
+        <v>41736.20655429615</v>
       </c>
       <c r="CU52" s="74">
         <f t="shared" si="108"/>
-        <v>52709.995913731786</v>
+        <v>51839.582095707061</v>
       </c>
       <c r="CV52" s="74">
         <f t="shared" si="108"/>
-        <v>64868.722849235695</v>
+        <v>63585.18376082863</v>
       </c>
       <c r="CW52" s="74">
         <f t="shared" si="108"/>
-        <v>78597.391413426609</v>
+        <v>76793.787977237254</v>
       </c>
       <c r="CX52" s="74">
         <f t="shared" si="108"/>
-        <v>94196.2984358377</v>
+        <v>91746.284604940709</v>
       </c>
       <c r="CY52" s="74">
         <f t="shared" si="108"/>
-        <v>112304.89783638441</v>
+        <v>109055.5470058404</v>
       </c>
       <c r="CZ52" s="74">
         <f t="shared" si="108"/>
-        <v>133172.63952072381</v>
+        <v>128945.11135937195</v>
       </c>
       <c r="DA52" s="74">
         <f t="shared" si="108"/>
-        <v>157099.00707913574</v>
+        <v>151688.29568787711</v>
       </c>
     </row>
     <row r="53" spans="2:156" s="2" customFormat="1" ht="15">
@@ -24648,239 +24642,239 @@
       </c>
       <c r="CR53" s="75">
         <f>CR51-CR52</f>
-        <v>125203.36592274104</v>
+        <v>125129.70122274105</v>
       </c>
       <c r="CS53" s="75">
         <f t="shared" ref="CS53:DA53" si="111">CS51-CS52</f>
-        <v>156848.92700537495</v>
+        <v>155360.89465229106</v>
       </c>
       <c r="CT53" s="75">
         <f t="shared" si="111"/>
-        <v>192656.48867170891</v>
+        <v>190131.60763623804</v>
       </c>
       <c r="CU53" s="75">
         <f t="shared" si="111"/>
-        <v>240123.31471811151</v>
+        <v>236158.09621377662</v>
       </c>
       <c r="CV53" s="75">
         <f t="shared" si="111"/>
-        <v>295513.07075762929</v>
+        <v>289665.83713266376</v>
       </c>
       <c r="CW53" s="75">
         <f t="shared" si="111"/>
-        <v>358054.78310561011</v>
+        <v>349838.36745185859</v>
       </c>
       <c r="CX53" s="75">
         <f t="shared" si="111"/>
-        <v>429116.47065214952</v>
+        <v>417955.29653361882</v>
       </c>
       <c r="CY53" s="75">
         <f t="shared" si="111"/>
-        <v>511611.20125464007</v>
+        <v>496808.60302660632</v>
       </c>
       <c r="CZ53" s="75">
         <f t="shared" si="111"/>
-        <v>606675.35781663074</v>
+        <v>587416.61841491668</v>
       </c>
       <c r="DA53" s="75">
         <f t="shared" si="111"/>
-        <v>715673.25447161845</v>
+        <v>691024.45813366247</v>
       </c>
       <c r="DB53" s="34">
         <f>DA53*(1+DA67)</f>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DC53" s="34">
         <f t="shared" ref="DC53:EX53" si="112">DB53*(1+DB67)</f>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DD53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DE53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DF53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DG53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DH53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DI53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DJ53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DK53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DL53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DM53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DN53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DO53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DP53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DQ53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DR53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DS53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DT53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DU53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DV53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DW53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DX53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DY53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="DZ53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EA53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EB53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EC53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="ED53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EE53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EF53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EG53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EH53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EI53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EJ53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EK53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EL53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EM53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EN53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EO53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EP53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EQ53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="ER53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="ES53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="ET53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EU53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EV53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EW53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EX53" s="34">
         <f t="shared" si="112"/>
-        <v>729986.71956105088</v>
+        <v>704844.94729633571</v>
       </c>
       <c r="EY53" s="34"/>
       <c r="EZ53" s="34"/>
@@ -27927,43 +27921,43 @@
       </c>
       <c r="CR64" s="74">
         <f>CQ64+CR53</f>
-        <v>161137.36592274104</v>
+        <v>161063.70122274105</v>
       </c>
       <c r="CS64" s="74">
         <f t="shared" ref="CS64:DA64" si="133">CR64+CS53</f>
-        <v>317986.29292811599</v>
+        <v>316424.59587503213</v>
       </c>
       <c r="CT64" s="74">
         <f t="shared" si="133"/>
-        <v>510642.7815998249</v>
+        <v>506556.20351127017</v>
       </c>
       <c r="CU64" s="74">
         <f t="shared" si="133"/>
-        <v>750766.09631793643</v>
+        <v>742714.29972504685</v>
       </c>
       <c r="CV64" s="74">
         <f t="shared" si="133"/>
-        <v>1046279.1670755658</v>
+        <v>1032380.1368577105</v>
       </c>
       <c r="CW64" s="74">
         <f t="shared" si="133"/>
-        <v>1404333.950181176</v>
+        <v>1382218.504309569</v>
       </c>
       <c r="CX64" s="74">
         <f t="shared" si="133"/>
-        <v>1833450.4208333255</v>
+        <v>1800173.8008431878</v>
       </c>
       <c r="CY64" s="74">
         <f t="shared" si="133"/>
-        <v>2345061.6220879657</v>
+        <v>2296982.4038697942</v>
       </c>
       <c r="CZ64" s="74">
         <f t="shared" si="133"/>
-        <v>2951736.9799045967</v>
+        <v>2884399.0222847108</v>
       </c>
       <c r="DA64" s="74">
         <f t="shared" si="133"/>
-        <v>3667410.2343762154</v>
+        <v>3575423.4804183734</v>
       </c>
     </row>
     <row r="65" spans="2:156">
@@ -28172,7 +28166,7 @@
         <v>173</v>
       </c>
       <c r="DA66" s="51">
-        <v>0.20499999999999999</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="DB66" s="48"/>
     </row>
@@ -28981,9 +28975,9 @@
       <c r="CZ73" s="50" t="s">
         <v>180</v>
       </c>
-      <c r="DA73" s="77">
+      <c r="DA73" s="76">
         <f>NPV(DA71,CR53:EO53)</f>
-        <v>4789000.8133773282</v>
+        <v>4646193.2668503616</v>
       </c>
       <c r="DB73" s="76"/>
       <c r="DC73" s="34"/>
@@ -29159,7 +29153,7 @@
       </c>
       <c r="DA75" s="56">
         <f>DA73/DA74</f>
-        <v>322.70894968849922</v>
+        <v>313.08579965298935</v>
       </c>
       <c r="DB75" s="47"/>
     </row>
@@ -29266,7 +29260,7 @@
       </c>
       <c r="DA76" s="56">
         <f>Main!C3</f>
-        <v>284.22000000000003</v>
+        <v>259.37</v>
       </c>
       <c r="DB76" s="57"/>
     </row>
@@ -29373,7 +29367,7 @@
       </c>
       <c r="DA77" s="51">
         <f>DA75/DA76-1</f>
-        <v>0.13541956825170365</v>
+        <v>0.20710105121251243</v>
       </c>
       <c r="DB77" s="58" t="str">
         <f>IF(DA77&gt;0,"Upside","Downside")</f>
@@ -29471,11 +29465,11 @@
         <f t="shared" si="147"/>
         <v>1995</v>
       </c>
-      <c r="CZ78" s="78" t="str" cm="1">
+      <c r="CZ78" s="77" t="str" cm="1">
         <f t="array" ref="CZ78">_xlfn.IFS(DA77&gt;=25%,"Strong Buy",DA77&gt;=10.00001%,"Buy",AND(DA77&lt;=10%,DA77&gt;=-4.9999%),"Hold",AND(DA77&lt;=-5%,DA77&gt;=-14.999999%),"Sell",DA77&lt;=-15%,"Strong Sell")</f>
         <v>Buy</v>
       </c>
-      <c r="DA78" s="78"/>
+      <c r="DA78" s="77"/>
     </row>
     <row r="79" spans="2:156" ht="13.5" customHeight="1">
       <c r="B79" s="1" t="s">
